--- a/bench/results/jmeter_S3_analysis.xlsx
+++ b/bench/results/jmeter_S3_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F3F608-4167-4085-ACE9-48E0FF0BEBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C690C1B-7258-4120-A180-AAD3400BF00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="7080" windowWidth="19410" windowHeight="10545" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,22 +63,22 @@
     <t>Scenario 3 Benchmark Results - POST /api/items</t>
   </si>
   <si>
-    <t>Average Response Time vs Concurrent Users (Scenario 3)</t>
-  </si>
-  <si>
-    <t>95th Percentile Response Time vs Concurrent Users (Scenario 3)</t>
-  </si>
-  <si>
-    <t>Median Response Time vs Concurrent Users (Scenario 3)</t>
-  </si>
-  <si>
-    <t>Throughput vs Concurrent Users (Scenario 3)</t>
-  </si>
-  <si>
     <t>Apache HTTP Server Memory Usage (MB) (Scenario 3)</t>
   </si>
   <si>
     <t>Samples</t>
+  </si>
+  <si>
+    <t>Average Response Time vs Number of Requests (Scenario 3)</t>
+  </si>
+  <si>
+    <t>95th Percentile Response Time vs Number of Requests (Scenario 3)</t>
+  </si>
+  <si>
+    <t>Median Response Time vs Number of Requests (Scenario 3)</t>
+  </si>
+  <si>
+    <t>Throughput vs Number of Requests (Scenario 3)</t>
   </si>
 </sst>
 </file>
@@ -7381,21 +7381,21 @@
       </c>
       <c r="D1" s="5"/>
       <c r="I1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="Q1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="Y1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>1</v>
@@ -7421,7 +7421,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>6</v>
@@ -7436,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>6</v>
@@ -7451,7 +7451,7 @@
         <v>9</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z2" s="8" t="s">
         <v>6</v>
@@ -8016,15 +8016,15 @@
     </row>
     <row r="20" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I20" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I21" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>6</v>
@@ -8039,7 +8039,7 @@
         <v>9</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P21" s="8" t="s">
         <v>6</v>

--- a/bench/results/jmeter_S3_analysis.xlsx
+++ b/bench/results/jmeter_S3_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C690C1B-7258-4120-A180-AAD3400BF00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8404F723-F280-4DD0-9EE2-4762A652EFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="7080" windowWidth="19410" windowHeight="10545" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/bench/results/jmeter_S3_analysis.xlsx
+++ b/bench/results/jmeter_S3_analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8404F723-F280-4DD0-9EE2-4762A652EFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACEDE1-79A9-4470-A65B-C404B1AC96F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3585,16 +3585,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>39.950000000000003</c:v>
+                  <c:v>41.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41.05</c:v>
+                  <c:v>43.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41.05</c:v>
+                  <c:v>46.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>41.35</c:v>
+                  <c:v>49.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3672,16 +3672,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>35.5</c:v>
+                  <c:v>36.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35.5</c:v>
+                  <c:v>36.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35.5</c:v>
+                  <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>35.5</c:v>
+                  <c:v>38.200000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3759,16 +3759,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>39.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.85</c:v>
+                  <c:v>41.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.85</c:v>
+                  <c:v>44.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40.85</c:v>
+                  <c:v>47.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3846,16 +3846,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>37.75</c:v>
+                  <c:v>38.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>37.75</c:v>
+                  <c:v>39.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.75</c:v>
+                  <c:v>41.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.75</c:v>
+                  <c:v>43.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8074,16 +8074,16 @@
         <v>100</v>
       </c>
       <c r="P22" s="6">
-        <v>39.950000000000003</v>
+        <v>41.5</v>
       </c>
       <c r="Q22" s="6">
-        <v>35.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="R22" s="6">
-        <v>38</v>
+        <v>39.5</v>
       </c>
       <c r="S22" s="6">
-        <v>37.75</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8106,16 +8106,16 @@
         <v>1000</v>
       </c>
       <c r="P23" s="6">
-        <v>41.05</v>
+        <v>43.8</v>
       </c>
       <c r="Q23" s="6">
-        <v>35.5</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="R23" s="6">
-        <v>40.85</v>
+        <v>41.8</v>
       </c>
       <c r="S23" s="6">
-        <v>37.75</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8138,16 +8138,16 @@
         <v>5000</v>
       </c>
       <c r="P24" s="6">
-        <v>41.05</v>
+        <v>46.2</v>
       </c>
       <c r="Q24" s="6">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
       <c r="R24" s="6">
-        <v>40.85</v>
+        <v>44.1</v>
       </c>
       <c r="S24" s="6">
-        <v>37.75</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8170,16 +8170,16 @@
         <v>10000</v>
       </c>
       <c r="P25" s="6">
-        <v>41.35</v>
+        <v>49.5</v>
       </c>
       <c r="Q25" s="6">
-        <v>35.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="R25" s="6">
-        <v>40.85</v>
+        <v>47.3</v>
       </c>
       <c r="S25" s="6">
-        <v>37.75</v>
+        <v>43.1</v>
       </c>
     </row>
   </sheetData>
